--- a/config/sla_targets.xlsx
+++ b/config/sla_targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,16 @@
           <t>Scenario: Peak Load (200 Users):Target Error Rate (%)</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Scenario: Spike Load (500 Users):Target RT (ms)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Scenario: Spike Load (500 Users):Target Error Rate (%)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -498,22 +508,28 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5</v>
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TC01_Launch</t>
+          <t>TC01_T_01_Launch_Homepage</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -532,32 +548,38 @@
         <v>300</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>550</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC02_Checkout</t>
+          <t>TC01_T_02_Navigate_Catalog</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>100</v>
@@ -569,18 +591,2002 @@
         <v>300</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>300</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>450</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>660</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TC01_T_03_Select_Fish_Category</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F5" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>300</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>450</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>660</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TC01_T_04_Select_Dogs_Category</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>300</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>300</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>450</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>660</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TC01_T_05_Select_Reptiles_Category</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>300</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>300</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>450</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>660</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC01_T_06_Select_Cats_Category</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>300</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>200</v>
+      </c>
+      <c r="F8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>300</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>450</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>660</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TC01_T_07_Select_Birds_Category</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>300</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" t="n">
+        <v>300</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>300</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>450</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>660</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC01_T_08_View_Product_Details_Angelfish</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>450</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>200</v>
+      </c>
+      <c r="F10" t="n">
+        <v>300</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>450</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>675</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>990</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC01_T_09_View_Product_Details_Bulldog</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>450</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>200</v>
+      </c>
+      <c r="F11" t="n">
+        <v>300</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>450</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>675</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>990</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC01_T_10_View_Product_Details_Iguana</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>450</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>200</v>
+      </c>
+      <c r="F12" t="n">
+        <v>300</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>450</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>675</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>990</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC01_T_11_Check_Item_Availability</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>450</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>450</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>675</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>990</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC01_T_12_Return_To_Main_Catalog</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>400</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>200</v>
+      </c>
+      <c r="F14" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>400</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>600</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>880</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC02_T_01_Launch_Shopping_Catalog</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>250</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>200</v>
+      </c>
+      <c r="F15" t="n">
+        <v>300</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>250</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>375</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>550</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC02_T_02_Select_Reptiles_Section</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>300</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>200</v>
+      </c>
+      <c r="F16" t="n">
+        <v>300</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>300</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>450</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>660</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC02_T_03_Select_Dogs_Section</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>300</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="n">
+        <v>200</v>
+      </c>
+      <c r="F17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>300</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>450</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>660</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TC02_T_04_View_Bulldog_Item</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>450</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F18" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>450</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>675</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>990</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TC02_T_05_Add_Bulldog_To_Cart</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="n">
+        <v>200</v>
+      </c>
+      <c r="F19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>600</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>900</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1320</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TC02_T_06_Select_Birds_Section</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>300</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>200</v>
+      </c>
+      <c r="F20" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>300</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>450</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>660</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TC02_T_07_View_Parrot_Item</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>450</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" t="n">
+        <v>200</v>
+      </c>
+      <c r="F21" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>450</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>675</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>990</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TC02_T_08_Add_Parrot_To_Cart</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>600</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="n">
+        <v>200</v>
+      </c>
+      <c r="F22" t="n">
+        <v>300</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>600</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>900</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1320</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TC02_T_09_Update_Cart_Quantities</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>600</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>200</v>
+      </c>
+      <c r="F23" t="n">
+        <v>300</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>600</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>900</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1320</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TC02_T_10_Apply_Coupon_Code</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>400</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="n">
+        <v>200</v>
+      </c>
+      <c r="F24" t="n">
+        <v>300</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>400</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>600</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>880</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TC02_T_11_Remove_Item_From_Cart</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>450</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>100</v>
+      </c>
+      <c r="E25" t="n">
+        <v>200</v>
+      </c>
+      <c r="F25" t="n">
+        <v>300</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>450</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>675</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>990</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TC02_T_12_Proceed_To_Checkout_Screen</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>600</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>100</v>
+      </c>
+      <c r="E26" t="n">
+        <v>200</v>
+      </c>
+      <c r="F26" t="n">
+        <v>300</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>600</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>900</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1320</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TC03_T_01_Launch_Search_Portal</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>250</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" t="n">
+        <v>200</v>
+      </c>
+      <c r="F27" t="n">
+        <v>300</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>250</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>375</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>550</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TC03_T_02_Search_Keyword_Bulldog</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>450</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" t="n">
+        <v>200</v>
+      </c>
+      <c r="F28" t="n">
+        <v>300</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>450</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>675</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>990</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TC03_T_03_Filter_Bulldog_Results</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>400</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" t="n">
+        <v>200</v>
+      </c>
+      <c r="F29" t="n">
+        <v>300</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>400</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>600</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>880</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TC03_T_04_Search_Keyword_Fish</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>450</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>100</v>
+      </c>
+      <c r="E30" t="n">
+        <v>200</v>
+      </c>
+      <c r="F30" t="n">
+        <v>300</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>450</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>675</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>990</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TC03_T_05_View_Fish_Search_Result</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>450</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" t="n">
+        <v>200</v>
+      </c>
+      <c r="F31" t="n">
+        <v>300</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>450</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>675</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>990</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TC03_T_06_Search_Keyword_Cat</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>450</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" t="n">
+        <v>200</v>
+      </c>
+      <c r="F32" t="n">
+        <v>300</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>450</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>675</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>990</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TC03_T_07_Search_Keyword_Poodle</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>450</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" t="n">
+        <v>200</v>
+      </c>
+      <c r="F33" t="n">
+        <v>300</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>450</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>675</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>990</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TC03_T_08_Search_Keyword_Snake</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>450</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>100</v>
+      </c>
+      <c r="E34" t="n">
+        <v>200</v>
+      </c>
+      <c r="F34" t="n">
+        <v>300</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>450</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>675</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>990</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TC03_T_09_Search_Keyword_Amazon</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>450</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" t="n">
+        <v>200</v>
+      </c>
+      <c r="F35" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>450</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>675</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>990</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TC03_T_10_Search_Special_Character_Query</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>450</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>100</v>
+      </c>
+      <c r="E36" t="n">
+        <v>200</v>
+      </c>
+      <c r="F36" t="n">
+        <v>300</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>450</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>675</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>990</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TC03_T_11_Search_Nonexistent_Product</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>450</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>100</v>
+      </c>
+      <c r="E37" t="n">
+        <v>200</v>
+      </c>
+      <c r="F37" t="n">
+        <v>300</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>450</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>675</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" t="n">
+        <v>990</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TC03_T_12_Clear_Search_And_Reset</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>450</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" t="n">
+        <v>200</v>
+      </c>
+      <c r="F38" t="n">
+        <v>300</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>450</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>675</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>990</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TC04_T_01_Launch_Authentication_Gateway</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>250</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>100</v>
+      </c>
+      <c r="E39" t="n">
+        <v>200</v>
+      </c>
+      <c r="F39" t="n">
+        <v>300</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>250</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>375</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>550</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TC04_T_02_Navigate_To_Signon_Page</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>300</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" t="n">
+        <v>200</v>
+      </c>
+      <c r="F40" t="n">
+        <v>300</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>300</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>450</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>660</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC04_T_03_Submit_Valid_Login_Credentials</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
         <v>500</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>100</v>
+      </c>
+      <c r="E41" t="n">
+        <v>200</v>
+      </c>
+      <c r="F41" t="n">
+        <v>300</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>500</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>750</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1100</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC04_T_04_View_User_Account_Profile</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>400</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>100</v>
+      </c>
+      <c r="E42" t="n">
+        <v>200</v>
+      </c>
+      <c r="F42" t="n">
+        <v>300</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>400</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>600</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>880</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TC04_T_05_Update_Account_Preferences</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>400</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>100</v>
+      </c>
+      <c r="E43" t="n">
+        <v>200</v>
+      </c>
+      <c r="F43" t="n">
+        <v>300</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>400</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>600</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>880</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TC04_T_06_View_Past_Order_History</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>750</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>100</v>
+      </c>
+      <c r="E44" t="n">
+        <v>200</v>
+      </c>
+      <c r="F44" t="n">
+        <v>300</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>750</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1125</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1650</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TC04_T_07_View_Specific_Order_Details</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>750</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>100</v>
+      </c>
+      <c r="E45" t="n">
+        <v>200</v>
+      </c>
+      <c r="F45" t="n">
+        <v>300</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>750</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1125</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1650</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TC04_T_08_View_Saved_Payment_Methods</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>750</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>100</v>
+      </c>
+      <c r="E46" t="n">
+        <v>200</v>
+      </c>
+      <c r="F46" t="n">
+        <v>300</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>750</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1125</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1650</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TC04_T_09_View_Saved_Addresses</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>400</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" t="n">
+        <v>200</v>
+      </c>
+      <c r="F47" t="n">
+        <v>300</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>400</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>600</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>880</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TC04_T_10_View_Wishlist_Items</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>450</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" t="n">
+        <v>200</v>
+      </c>
+      <c r="F48" t="n">
+        <v>300</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>450</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>675</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2</v>
+      </c>
+      <c r="L48" t="n">
+        <v>990</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TC04_T_11_Perform_User_Sign_Out</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>400</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>100</v>
+      </c>
+      <c r="E49" t="n">
+        <v>200</v>
+      </c>
+      <c r="F49" t="n">
+        <v>300</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>400</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>600</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>880</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TC04_T_12_Return_To_Public_Homepage</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>250</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" t="n">
+        <v>200</v>
+      </c>
+      <c r="F50" t="n">
+        <v>300</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>250</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>375</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2</v>
+      </c>
+      <c r="L50" t="n">
+        <v>550</v>
+      </c>
+      <c r="M50" t="n">
         <v>3</v>
       </c>
     </row>
